--- a/InputData/bldgs/FoBObE/Frac of Bldgs Owned by Entity.xlsx
+++ b/InputData/bldgs/FoBObE/Frac of Bldgs Owned by Entity.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\bldgs\FoBObE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-dc-replay\InputData\bldgs\FoBObE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5D1B2A-0F82-4946-A7E8-65637F63812F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC811776-CEE9-45CB-96A3-3AA8978EC456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16455" yWindow="150" windowWidth="29520" windowHeight="21060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Residential" sheetId="2" r:id="rId2"/>
     <sheet name="Commercial" sheetId="3" r:id="rId3"/>
-    <sheet name="FoBObE" sheetId="4" r:id="rId4"/>
+    <sheet name="Data Centers" sheetId="5" r:id="rId4"/>
+    <sheet name="FoBObE" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="outputfrac_bio">#REF!</definedName>
@@ -35,6 +36,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="82">
   <si>
     <t>Sources:</t>
   </si>
@@ -243,6 +246,51 @@
   </si>
   <si>
     <t>domestic industries</t>
+  </si>
+  <si>
+    <t>Data center assumptions</t>
+  </si>
+  <si>
+    <t>Data centers are a separate building type. Unlike commercial buildings, which include schools, hospitals and government offices, data centers are owned by businesses.</t>
+  </si>
+  <si>
+    <t>Assumption</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Basis</t>
+  </si>
+  <si>
+    <t>Share of data centers owned by government</t>
+  </si>
+  <si>
+    <t>Data centers are businesses.</t>
+  </si>
+  <si>
+    <t>Share owned by domestic industries</t>
+  </si>
+  <si>
+    <t>All data-center capital and energy bills are booked to domestic (nonenergy) industries.</t>
+  </si>
+  <si>
+    <t>Share owned by labor and consumers</t>
+  </si>
+  <si>
+    <t>Share owned by foreign entities</t>
+  </si>
+  <si>
+    <t>Treated as domestic, like the other building types.</t>
+  </si>
+  <si>
+    <t>Data Centers</t>
+  </si>
+  <si>
+    <t>Data centers</t>
+  </si>
+  <si>
+    <t>Data centers are owned entirely by domestic industries; see the 'Data Centers' tab.</t>
   </si>
 </sst>
 </file>
@@ -253,7 +301,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.00000000"/>
+    <numFmt numFmtId="166" formatCode="0.00000000"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -511,7 +559,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -523,16 +571,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -542,15 +589,15 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -583,30 +630,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -618,9 +658,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -633,16 +675,13 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -654,8 +693,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -678,9 +723,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -718,9 +763,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -753,26 +798,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -805,26 +833,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -998,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -1074,24 +1085,32 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="63" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1122,20 +1141,20 @@
       <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="62"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
@@ -1163,173 +1182,173 @@
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="8"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="63" t="s">
+      <c r="G5" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
       <c r="J5" s="9"/>
-      <c r="K5" s="63" t="s">
+      <c r="K5" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
       <c r="N5" s="9"/>
-      <c r="O5" s="64" t="s">
+      <c r="O5" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="P5" s="64"/>
-      <c r="Q5" s="65"/>
+      <c r="P5" s="55"/>
+      <c r="Q5" s="56"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="9"/>
-      <c r="C6" s="66" t="s">
+      <c r="C6" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
       <c r="F6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="66" t="s">
+      <c r="G6" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="66" t="s">
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="66" t="s">
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="P6" s="66"/>
-      <c r="Q6" s="67"/>
+      <c r="P6" s="57"/>
+      <c r="Q6" s="58"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
-      <c r="D7" s="16">
+      <c r="D7" s="15">
         <v>54.92</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="16">
+      <c r="E7" s="16"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="15">
         <v>104.45</v>
       </c>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="16">
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="15">
         <v>40.328185328185334</v>
       </c>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
       <c r="O7" s="9"/>
-      <c r="P7" s="18">
+      <c r="P7" s="17">
         <v>0.7816091954022989</v>
       </c>
       <c r="Q7" s="10"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <v>77.42</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16">
+      <c r="E8" s="16"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15">
         <v>71.67</v>
       </c>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="16">
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="15">
         <v>28.44047619047619</v>
       </c>
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
       <c r="O8" s="9"/>
-      <c r="P8" s="18">
+      <c r="P8" s="17">
         <v>0.21839080459770113</v>
       </c>
       <c r="Q8" s="10"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <v>75.709999999999994</v>
       </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16">
+      <c r="E9" s="16"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15">
         <v>62.67</v>
       </c>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="16">
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="15">
         <v>28.747706422018346</v>
       </c>
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
       <c r="O9" s="9"/>
-      <c r="P9" s="20">
+      <c r="P9" s="19">
         <v>2.4904214559386975E-2</v>
       </c>
       <c r="Q9" s="10"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
-      <c r="D10" s="16">
+      <c r="D10" s="15">
         <v>77.650000000000006</v>
       </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16">
+      <c r="E10" s="16"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15">
         <v>73.040000000000006</v>
       </c>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="16">
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="15">
         <v>28.420233463035025</v>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
       <c r="O10" s="9"/>
-      <c r="P10" s="21">
+      <c r="P10" s="20">
         <v>0.1934865900383142</v>
       </c>
       <c r="Q10" s="10"/>
@@ -1350,7 +1369,7 @@
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
       <c r="O11" s="9"/>
-      <c r="P11" s="18">
+      <c r="P11" s="17">
         <v>1</v>
       </c>
       <c r="Q11" s="10"/>
@@ -1371,92 +1390,92 @@
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
       <c r="O12" s="9"/>
-      <c r="P12" s="22"/>
+      <c r="P12" s="21"/>
       <c r="Q12" s="10"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="58"/>
-      <c r="Q13" s="59"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="50"/>
+      <c r="Q13" s="51"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="23"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="58"/>
-      <c r="O14" s="58"/>
-      <c r="P14" s="58"/>
-      <c r="Q14" s="59"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="50"/>
+      <c r="K14" s="50"/>
+      <c r="L14" s="50"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="50"/>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="51"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="23"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="58"/>
-      <c r="M15" s="58"/>
-      <c r="N15" s="58"/>
-      <c r="O15" s="58"/>
-      <c r="P15" s="58"/>
-      <c r="Q15" s="59"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="50"/>
+      <c r="K15" s="50"/>
+      <c r="L15" s="50"/>
+      <c r="M15" s="50"/>
+      <c r="N15" s="50"/>
+      <c r="O15" s="50"/>
+      <c r="P15" s="50"/>
+      <c r="Q15" s="51"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="60" t="s">
+      <c r="B16" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="60"/>
-      <c r="N16" s="60"/>
-      <c r="O16" s="60"/>
-      <c r="P16" s="60"/>
-      <c r="Q16" s="61"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="52"/>
+      <c r="N16" s="52"/>
+      <c r="O16" s="52"/>
+      <c r="P16" s="52"/>
+      <c r="Q16" s="53"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -1477,7 +1496,7 @@
         <f t="shared" ref="B21:B23" si="0">A7</f>
         <v>Owned</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="25">
         <f>(P7/D7)/SUM(P$7/D$7,P$9/D$9,P$10/D$10)</f>
         <v>0.83458607438155852</v>
       </c>
@@ -1487,30 +1506,30 @@
         <f t="shared" si="0"/>
         <v>Rented</v>
       </c>
-      <c r="C22" s="26"/>
+      <c r="C22" s="25"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="25" t="str">
+      <c r="B23" s="24" t="str">
         <f t="shared" si="0"/>
         <v>Public Housing</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="25">
         <f>(P9/D9)/SUM(P$7/D$7,P$9/D$9,P$10/D$10)</f>
         <v>1.9289972368294446E-2</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="25" t="str">
+      <c r="B24" s="24" t="str">
         <f>A10</f>
         <v>Not Public Housing</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="25">
         <f>(P10/D10)/SUM(P$7/D$7,P$9/D$9,P$10/D$10)</f>
         <v>0.14612395325014693</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C25" s="26">
+      <c r="C25" s="25">
         <f>SUM(C21:C24)</f>
         <v>0.99999999999999989</v>
       </c>
@@ -1534,7 +1553,7 @@
       <c r="B30" t="s">
         <v>54</v>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="26">
         <v>0.75</v>
       </c>
     </row>
@@ -1542,43 +1561,43 @@
       <c r="B31" t="s">
         <v>29</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="26">
         <f>1-G30</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="28" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="30" t="s">
+      <c r="B34" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="31">
         <f>C23</f>
         <v>1.9289972368294446E-2</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="30" t="s">
+      <c r="B35" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="32">
         <f>C24*G31</f>
         <v>3.6530988312536733E-2</v>
       </c>
     </row>
     <row r="36" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="31" t="s">
+      <c r="B36" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="33">
         <f>C21+(C24*G30)</f>
         <v>0.94417903931916869</v>
       </c>
@@ -1616,375 +1635,375 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="38"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="7"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="41"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="10"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="43" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="44"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="37"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="45">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="38">
         <v>0.4010403803408249</v>
       </c>
-      <c r="E6" s="40"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="46" t="s">
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="47">
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="40">
         <v>0.76285811311434926</v>
       </c>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="41"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="10"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="45">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="38">
         <v>0.25114225734749318</v>
       </c>
-      <c r="E7" s="40"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="48" t="s">
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="49">
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="19">
         <v>0.36414855519881451</v>
       </c>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="41"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="10"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="45">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="38">
         <v>0.11578476166954804</v>
       </c>
-      <c r="E8" s="40"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="48" t="s">
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="49">
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="19">
         <v>0.36913435416152135</v>
       </c>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="41"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="10"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="45">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="38">
         <v>0.15567115337120277</v>
       </c>
-      <c r="E9" s="40"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="48" t="s">
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="49">
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="19">
         <v>2.9575203754013336E-2</v>
       </c>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="41"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="10"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="51">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="43">
         <v>7.6361447270931096E-2</v>
       </c>
-      <c r="E10" s="40"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="46" t="s">
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="47">
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="40">
         <v>0.23714188688565077</v>
       </c>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="41"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="10"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="45">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="38">
         <v>1</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="48" t="s">
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="45">
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="38">
         <v>3.0192640158063718E-2</v>
       </c>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="41"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="10"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="39"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="48" t="s">
+      <c r="A12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="H12" s="52"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="45">
+      <c r="H12" s="44"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="38">
         <v>4.8779945665596444E-2</v>
       </c>
-      <c r="L12" s="40"/>
-      <c r="M12" s="40"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="41"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="10"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="39"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="53" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="51">
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="43">
         <v>0.14816930106199061</v>
       </c>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="49"/>
-      <c r="Q13" s="41"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="10"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="39"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="52" t="s">
+      <c r="A14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="49">
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="19">
         <v>1</v>
       </c>
-      <c r="L14" s="40"/>
-      <c r="M14" s="40"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="49"/>
-      <c r="Q14" s="41"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="10"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="39"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="41"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="10"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="68" t="s">
+      <c r="B16" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="68"/>
-      <c r="L16" s="68"/>
-      <c r="M16" s="68"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="68"/>
-      <c r="P16" s="68"/>
-      <c r="Q16" s="69"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="59"/>
+      <c r="K16" s="59"/>
+      <c r="L16" s="59"/>
+      <c r="M16" s="59"/>
+      <c r="N16" s="59"/>
+      <c r="O16" s="59"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="60"/>
     </row>
     <row r="18" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="28" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="31">
         <f>K10</f>
         <v>0.23714188688565077</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="32">
         <f>K6</f>
         <v>0.76285811311434926</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="33">
         <v>0</v>
       </c>
     </row>
@@ -1997,11 +2016,162 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF35421C-4603-4F49-807C-23F92D8E07DA}">
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="90.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="61" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7" s="61" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8" s="61" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" s="61"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" s="61"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" s="61"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" s="61"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="61"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" s="61"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C15" s="61"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" s="61"/>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="61"/>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="61"/>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="61"/>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="61"/>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="61"/>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C22" s="61"/>
+    </row>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="61"/>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C24" s="61"/>
+    </row>
+    <row r="25" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C25" s="61"/>
+    </row>
+    <row r="26" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C26" s="61"/>
+    </row>
+    <row r="27" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C27" s="61"/>
+    </row>
+    <row r="28" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C28" s="61"/>
+    </row>
+    <row r="29" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C29" s="61"/>
+    </row>
+    <row r="30" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C30" s="61"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.28515625" customWidth="1"/>
@@ -2010,63 +2180,74 @@
     <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="47" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="57">
+      <c r="B2" s="48">
         <f>Residential!C34</f>
         <v>1.9289972368294446E-2</v>
       </c>
-      <c r="C2" s="57">
+      <c r="C2" s="48">
         <f>B2</f>
         <v>1.9289972368294446E-2</v>
       </c>
-      <c r="D2" s="57">
+      <c r="D2" s="48">
         <f>Commercial!C20</f>
         <v>0.23714188688565077</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <f>'Data Centers'!$B$5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="57">
+      <c r="B3" s="48">
         <f>Residential!C35</f>
         <v>3.6530988312536733E-2</v>
       </c>
-      <c r="C3" s="57">
+      <c r="C3" s="48">
         <f t="shared" ref="C3:C5" si="0">B3</f>
         <v>3.6530988312536733E-2</v>
       </c>
-      <c r="D3" s="57">
+      <c r="D3" s="48">
         <f>Commercial!$C$21</f>
         <v>0.76285811311434926</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <f>'Data Centers'!$B$6</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="57">
+      <c r="B4" s="48">
         <f>Residential!C36</f>
         <v>0.94417903931916869</v>
       </c>
-      <c r="C4" s="57">
+      <c r="C4" s="48">
         <f t="shared" si="0"/>
         <v>0.94417903931916869</v>
       </c>
@@ -2074,19 +2255,27 @@
         <f>Commercial!C22</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <f>'Data Centers'!$B$7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>59</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
-      <c r="C5" s="56">
+      <c r="C5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f>'Data Centers'!$B$8</f>
         <v>0</v>
       </c>
     </row>
